--- a/Data Analysis.xlsx
+++ b/Data Analysis.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d2fa71209959418/University of Toronto/Project/Galbraith-Building-Heat-Loss-Analysis/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A89B1F923E49C836C8DF9863C03DB0C1DB9DDA7B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1445815D-135B-4542-ADAE-8F0AE6B74BF9}"/>
+  <bookViews>
+    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -196,68 +218,69 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy h:mm"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="10.0"/>
+  <fonts count="22">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15.0"/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Montserrat"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Montserrat"/>
     </font>
     <font>
       <i/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Montserrat"/>
     </font>
     <font>
       <i/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
     <font>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -265,12 +288,16 @@
     <font>
       <b/>
       <i/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
-    <font/>
-    <font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -278,43 +305,50 @@
     <font>
       <b/>
       <i/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color rgb="FF1F1F1F"/>
       <name val="'Times New Roman'"/>
     </font>
     <font>
       <i/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color rgb="FF1F1F1F"/>
       <name val="'Times New Roman'"/>
     </font>
     <font>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color rgb="FF1F1F1F"/>
       <name val="'Times New Roman'"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
     </font>
   </fonts>
   <fills count="5">
@@ -322,7 +356,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -344,7 +378,13 @@
     </fill>
   </fills>
   <borders count="8">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -358,19 +398,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF660000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF660000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF660000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF660000"/>
       </right>
@@ -380,6 +424,7 @@
       <bottom style="thin">
         <color rgb="FF660000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -394,6 +439,7 @@
       <bottom style="thin">
         <color rgb="FF660000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -405,6 +451,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -413,6 +461,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -421,103 +472,78 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -528,11 +554,17 @@
     <xdr:ext cx="6915150" cy="4371975"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image1.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -556,11 +588,17 @@
     <xdr:ext cx="4686300" cy="3086100"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="3" name="image2.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -577,12 +615,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -772,35 +806,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B4:W59"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="30.5"/>
-    <col customWidth="1" min="3" max="3" width="16.0"/>
-    <col customWidth="1" min="4" max="4" width="12.5"/>
-    <col customWidth="1" min="5" max="5" width="12.13"/>
-    <col customWidth="1" min="6" max="6" width="25.13"/>
-    <col customWidth="1" min="7" max="7" width="21.75"/>
-    <col customWidth="1" min="8" max="8" width="22.88"/>
-    <col customWidth="1" min="9" max="9" width="12.5"/>
-    <col customWidth="1" min="10" max="10" width="20.75"/>
-    <col customWidth="1" min="11" max="11" width="20.88"/>
-    <col customWidth="1" min="12" max="12" width="21.38"/>
-    <col customWidth="1" min="15" max="15" width="25.0"/>
-    <col customWidth="1" min="16" max="16" width="11.38"/>
-    <col customWidth="1" min="17" max="17" width="12.13"/>
-    <col customWidth="1" min="20" max="20" width="25.0"/>
+    <col min="2" max="2" width="30.453125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" customWidth="1"/>
+    <col min="6" max="6" width="25.08984375" customWidth="1"/>
+    <col min="7" max="7" width="21.7265625" customWidth="1"/>
+    <col min="8" max="8" width="22.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="20.7265625" customWidth="1"/>
+    <col min="11" max="11" width="20.90625" customWidth="1"/>
+    <col min="12" max="12" width="21.36328125" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="16" max="16" width="11.36328125" customWidth="1"/>
+    <col min="17" max="17" width="12.08984375" customWidth="1"/>
+    <col min="20" max="20" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
+    <row r="4" spans="2:23" ht="15.75" customHeight="1">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -813,7 +850,7 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="2:23" ht="15.75" customHeight="1">
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
@@ -855,7 +892,7 @@
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
     </row>
-    <row r="6">
+    <row r="6" spans="2:23" ht="15.75" customHeight="1">
       <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
@@ -863,60 +900,60 @@
         <v>22.8</v>
       </c>
       <c r="D6" s="7">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="E6" s="7">
-        <v>20.4</v>
-      </c>
-      <c r="F6" s="8" t="s">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="7">
         <v>22.5</v>
       </c>
-      <c r="I6" s="9">
-        <f t="shared" ref="I6:I9" si="1">ABS(C6-H6)</f>
-        <v>0.3</v>
+      <c r="I6" s="7">
+        <f t="shared" ref="I6:I9" si="0">ABS(C6-H6)</f>
+        <v>0.30000000000000071</v>
       </c>
       <c r="J6" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" ref="K6:K9" si="2">G6*I6*J6</f>
-        <v>0.9</v>
-      </c>
-      <c r="L6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" ref="K6:K9" si="1">G6*I6*J6</f>
+        <v>0.90000000000000213</v>
+      </c>
+      <c r="L6" s="8">
         <v>46109.645833333336</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="R6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="T6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="U6" s="12" t="s">
+      <c r="U6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="V6" s="12" t="s">
+      <c r="V6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="W6" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:23" ht="15.75" customHeight="1">
       <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
@@ -929,7 +966,7 @@
       <c r="E7" s="7">
         <v>15.4</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="7">
@@ -938,51 +975,51 @@
       <c r="H7" s="7">
         <v>22.5</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7">
         <f t="shared" si="1"/>
-        <v>5.7</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="K7" s="9">
-        <f t="shared" si="2"/>
-        <v>32.49</v>
-      </c>
-      <c r="L7" s="10">
-        <v>46110.65833333333</v>
+        <v>32.489999999999995</v>
+      </c>
+      <c r="L7" s="8">
+        <v>46110.658333333333</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="11">
         <v>17.2</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="Q7" s="11">
         <v>16.8</v>
       </c>
-      <c r="R7" s="13">
-        <v>17.9</v>
+      <c r="R7" s="11">
+        <v>17.899999999999999</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="U7" s="13">
+      <c r="U7" s="11">
         <v>20.8</v>
       </c>
-      <c r="V7" s="13">
+      <c r="V7" s="11">
         <v>19.7</v>
       </c>
-      <c r="W7" s="13">
+      <c r="W7" s="11">
         <v>19.8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:23" ht="15.75" customHeight="1">
       <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="7">
-        <v>16.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D8" s="7">
         <v>22.6</v>
@@ -990,7 +1027,7 @@
       <c r="E8" s="7">
         <v>12.8</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="7">
@@ -999,46 +1036,46 @@
       <c r="H8" s="7">
         <v>22.5</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>6.1000000000000014</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7">
         <f t="shared" si="1"/>
-        <v>6.1</v>
-      </c>
-      <c r="J8" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="K8" s="9">
-        <f t="shared" si="2"/>
-        <v>17.08</v>
-      </c>
-      <c r="L8" s="10">
-        <v>46111.64791666667</v>
+        <v>17.080000000000002</v>
+      </c>
+      <c r="L8" s="8">
+        <v>46111.647916666669</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="11">
         <v>19.2</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="11">
         <v>18.7</v>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="11">
         <v>27.1</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="U8" s="13">
-        <v>21.0</v>
-      </c>
-      <c r="V8" s="13">
-        <v>20.0</v>
-      </c>
-      <c r="W8" s="13">
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="U8" s="11">
+        <v>21</v>
+      </c>
+      <c r="V8" s="11">
+        <v>20</v>
+      </c>
+      <c r="W8" s="11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" ht="15.75" customHeight="1">
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
@@ -1051,7 +1088,7 @@
       <c r="E9" s="7">
         <v>7.8</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="7">
@@ -1060,267 +1097,277 @@
       <c r="H9" s="7">
         <v>22.5</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>11.6</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7">
         <f t="shared" si="1"/>
-        <v>11.6</v>
-      </c>
-      <c r="J9" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="K9" s="9">
-        <f t="shared" si="2"/>
         <v>66.12</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="8">
         <v>46112.649305555555</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="11">
         <v>16.2</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="11">
         <v>15.4</v>
       </c>
-      <c r="R9" s="13">
+      <c r="R9" s="11">
         <v>16.5</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="13">
-        <v>20.4</v>
-      </c>
-      <c r="V9" s="13">
+      <c r="U9" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="V9" s="11">
         <v>19.2</v>
       </c>
-      <c r="W9" s="13">
+      <c r="W9" s="11">
         <v>19.2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B10" s="12" t="s">
         <v>24</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="11">
         <v>5.7</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="11">
         <v>5.7</v>
       </c>
-      <c r="R10" s="13">
+      <c r="R10" s="11">
         <v>5.7</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="V10" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="W10" s="13">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="15" t="s">
+      <c r="U10" s="11">
+        <v>2</v>
+      </c>
+      <c r="V10" s="11">
+        <v>2</v>
+      </c>
+      <c r="W10" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="C11" s="22"/>
+      <c r="J11" s="13"/>
       <c r="O11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="11">
         <v>22.5</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="11">
         <v>22.5</v>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="11">
         <v>22.5</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="13">
+      <c r="U11" s="11">
         <v>22.5</v>
       </c>
-      <c r="V11" s="13">
+      <c r="V11" s="11">
         <v>22.5</v>
       </c>
-      <c r="W11" s="13">
+      <c r="W11" s="11">
         <v>22.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="18" t="s">
+    <row r="12" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="14">
         <f>AVERAGE(K6:K9)</f>
-        <v>29.1475</v>
+        <v>29.147500000000001</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P12" s="19">
-        <f t="shared" ref="P12:R12" si="3">ABS(P11-P7)</f>
-        <v>5.3</v>
-      </c>
-      <c r="Q12" s="19">
-        <f t="shared" si="3"/>
-        <v>5.7</v>
-      </c>
-      <c r="R12" s="19">
-        <f t="shared" si="3"/>
-        <v>4.6</v>
+      <c r="P12" s="11">
+        <f t="shared" ref="P12:R12" si="2">ABS(P11-P7)</f>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="Q12" s="11">
+        <f t="shared" si="2"/>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="R12" s="11">
+        <f t="shared" si="2"/>
+        <v>4.6000000000000014</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="U12" s="19">
-        <f t="shared" ref="U12:W12" si="4">ABS(U11-U7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="V12" s="19">
-        <f t="shared" si="4"/>
-        <v>2.8</v>
-      </c>
-      <c r="W12" s="19">
-        <f t="shared" si="4"/>
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="18" t="s">
+      <c r="U12" s="11">
+        <f t="shared" ref="U12:W12" si="3">ABS(U11-U7)</f>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="V12" s="11">
+        <f t="shared" si="3"/>
+        <v>2.8000000000000007</v>
+      </c>
+      <c r="W12" s="11">
+        <f t="shared" si="3"/>
+        <v>2.6999999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B13" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="14">
         <f>STDEV(K6:K9)</f>
-        <v>27.81896161</v>
+        <v>27.818961608945791</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>1.0</v>
+      <c r="P13" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="U13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="V13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="W13" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="18" t="s">
+      <c r="U13" s="11">
+        <v>1</v>
+      </c>
+      <c r="V13" s="11">
+        <v>1</v>
+      </c>
+      <c r="W13" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B14" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="14">
         <f>C12+0.5*C13</f>
-        <v>43.0569808</v>
+        <v>43.0569808044729</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P14" s="19">
-        <f t="shared" ref="P14:R14" si="5">P13*P12*P10</f>
-        <v>30.21</v>
-      </c>
-      <c r="Q14" s="19">
-        <f t="shared" si="5"/>
-        <v>32.49</v>
-      </c>
-      <c r="R14" s="19">
-        <f t="shared" si="5"/>
-        <v>26.22</v>
+      <c r="P14" s="11">
+        <f t="shared" ref="P14:R14" si="4">P13*P12*P10</f>
+        <v>30.210000000000004</v>
+      </c>
+      <c r="Q14" s="11">
+        <f t="shared" si="4"/>
+        <v>32.489999999999995</v>
+      </c>
+      <c r="R14" s="11">
+        <f t="shared" si="4"/>
+        <v>26.22000000000001</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="U14" s="19">
-        <f t="shared" ref="U14:W14" si="6">U13*U12*U10</f>
-        <v>3.4</v>
-      </c>
-      <c r="V14" s="19">
-        <f t="shared" si="6"/>
-        <v>5.6</v>
-      </c>
-      <c r="W14" s="19">
-        <f t="shared" si="6"/>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="18" t="s">
+      <c r="U14" s="11">
+        <f t="shared" ref="U14:W14" si="5">U13*U12*U10</f>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="V14" s="11">
+        <f t="shared" si="5"/>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="W14" s="11">
+        <f t="shared" si="5"/>
+        <v>5.3999999999999986</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B15" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="14">
         <f>C12-0.5*C13</f>
-        <v>15.2380192</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="18" t="s">
+        <v>15.238019195527105</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23" ht="15.75" customHeight="1">
+      <c r="B16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="22" t="s">
+    <row r="18" spans="2:12">
+      <c r="B18" s="23" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="23" t="s">
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="17"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="23" t="s">
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="24"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="25" t="s">
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="22" spans="2:12" ht="15.75" customHeight="1">
+      <c r="B22" s="17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="25" t="s">
+    <row r="23" spans="2:12" ht="23">
+      <c r="B23" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="25" t="s">
+    <row r="24" spans="2:12" ht="23">
+      <c r="B24" s="17" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:12" ht="15.5">
       <c r="B31" s="2" t="s">
         <v>0</v>
       </c>
@@ -1351,24 +1398,24 @@
       <c r="K31" s="2"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32">
-      <c r="B32" s="6" t="s">
+    <row r="32" spans="2:12" ht="21.5">
+      <c r="B32" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
         <v>22.8</v>
       </c>
       <c r="D32" s="7">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="E32" s="7">
-        <v>20.4</v>
-      </c>
-      <c r="F32" s="8" t="s">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>39</v>
       </c>
       <c r="G32" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="7">
         <v>0.3</v>
@@ -1376,14 +1423,14 @@
       <c r="I32" s="7">
         <v>0.6</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="8">
         <v>46109.645833333336</v>
       </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="s">
+      <c r="K32" s="7"/>
+      <c r="L32" s="8"/>
+    </row>
+    <row r="33" spans="2:17" ht="21.5">
+      <c r="B33" s="29" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="7">
@@ -1395,7 +1442,7 @@
       <c r="E33" s="7">
         <v>15.4</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>40</v>
       </c>
       <c r="G33" s="7">
@@ -1407,18 +1454,18 @@
       <c r="I33" s="7">
         <v>32.5</v>
       </c>
-      <c r="J33" s="10">
-        <v>46110.65833333333</v>
-      </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="6" t="s">
+      <c r="J33" s="8">
+        <v>46110.658333333333</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="2:17" ht="21.5">
+      <c r="B34" s="29" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="7">
-        <v>16.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D34" s="7">
         <v>22.6</v>
@@ -1426,7 +1473,7 @@
       <c r="E34" s="7">
         <v>12.8</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="7" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="7">
@@ -1436,16 +1483,16 @@
         <v>6.1</v>
       </c>
       <c r="I34" s="7">
-        <v>17.1</v>
-      </c>
-      <c r="J34" s="10">
-        <v>46111.64791666667</v>
-      </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="s">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="J34" s="8">
+        <v>46111.647916666669</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="2:17" ht="21.5">
+      <c r="B35" s="29" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="7">
@@ -1457,7 +1504,7 @@
       <c r="E35" s="7">
         <v>7.8</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="7">
@@ -1467,161 +1514,161 @@
         <v>11.6</v>
       </c>
       <c r="I35" s="7">
-        <v>66.1</v>
-      </c>
-      <c r="J35" s="10">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="J35" s="8">
         <v>46112.649305555555</v>
       </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="10"/>
-    </row>
-    <row r="46">
-      <c r="O46" s="26" t="s">
+      <c r="K35" s="7"/>
+      <c r="L35" s="8"/>
+    </row>
+    <row r="46" spans="2:17" ht="86">
+      <c r="O46" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="P46" s="26" t="s">
+      <c r="P46" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="Q46" s="26" t="s">
+      <c r="Q46" s="18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47">
-      <c r="O47" s="27" t="s">
+    <row r="47" spans="2:17" ht="86">
+      <c r="O47" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="P47" s="28" t="s">
+      <c r="P47" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="Q47" s="29">
+      <c r="Q47" s="20">
         <v>5.7</v>
       </c>
     </row>
-    <row r="48">
-      <c r="O48" s="30"/>
-      <c r="P48" s="28" t="s">
+    <row r="48" spans="2:17" ht="86">
+      <c r="O48" s="27"/>
+      <c r="P48" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="Q48" s="29">
+      <c r="Q48" s="20">
         <v>4.8</v>
       </c>
     </row>
-    <row r="49">
-      <c r="O49" s="30"/>
-      <c r="P49" s="28" t="s">
+    <row r="49" spans="15:17" ht="86">
+      <c r="O49" s="27"/>
+      <c r="P49" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="Q49" s="29">
+      <c r="Q49" s="20">
         <v>4.8</v>
       </c>
     </row>
-    <row r="50">
-      <c r="O50" s="31"/>
-      <c r="P50" s="28" t="s">
+    <row r="50" spans="15:17" ht="86">
+      <c r="O50" s="28"/>
+      <c r="P50" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Q50" s="29">
+      <c r="Q50" s="20">
         <v>5.7</v>
       </c>
     </row>
-    <row r="51">
-      <c r="O51" s="27" t="s">
+    <row r="51" spans="15:17" ht="64.5">
+      <c r="O51" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="P51" s="28" t="s">
+      <c r="P51" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="Q51" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="O52" s="30"/>
-      <c r="P52" s="28" t="s">
+      <c r="Q51" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="15:17" ht="43">
+      <c r="O52" s="27"/>
+      <c r="P52" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="Q52" s="29">
+      <c r="Q52" s="20">
         <v>5.7</v>
       </c>
     </row>
-    <row r="53">
-      <c r="O53" s="31"/>
-      <c r="P53" s="28" t="s">
+    <row r="53" spans="15:17" ht="86">
+      <c r="O53" s="28"/>
+      <c r="P53" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="Q53" s="29">
+      <c r="Q53" s="20">
         <v>5.7</v>
       </c>
     </row>
-    <row r="54">
-      <c r="O54" s="27" t="s">
+    <row r="54" spans="15:17" ht="43">
+      <c r="O54" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="P54" s="28" t="s">
+      <c r="P54" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="Q54" s="29">
+      <c r="Q54" s="20">
         <v>2.1</v>
       </c>
     </row>
-    <row r="55">
-      <c r="O55" s="30"/>
-      <c r="P55" s="28" t="s">
+    <row r="55" spans="15:17" ht="43">
+      <c r="O55" s="27"/>
+      <c r="P55" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="Q55" s="29">
+      <c r="Q55" s="20">
         <v>2.25</v>
       </c>
     </row>
-    <row r="56">
-      <c r="O56" s="30"/>
-      <c r="P56" s="28" t="s">
+    <row r="56" spans="15:17" ht="64.5">
+      <c r="O56" s="27"/>
+      <c r="P56" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="Q56" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="O57" s="30"/>
-      <c r="P57" s="28" t="s">
+      <c r="Q56" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="15:17" ht="43">
+      <c r="O57" s="27"/>
+      <c r="P57" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="Q57" s="29">
+      <c r="Q57" s="20">
         <v>1.3</v>
       </c>
     </row>
-    <row r="58">
-      <c r="O58" s="30"/>
-      <c r="P58" s="28" t="s">
+    <row r="58" spans="15:17" ht="43">
+      <c r="O58" s="27"/>
+      <c r="P58" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="Q58" s="29">
+      <c r="Q58" s="20">
         <v>0.18</v>
       </c>
     </row>
-    <row r="59">
-      <c r="O59" s="31"/>
-      <c r="P59" s="28" t="s">
+    <row r="59" spans="15:17" ht="43">
+      <c r="O59" s="28"/>
+      <c r="P59" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="Q59" s="29">
+      <c r="Q59" s="20">
         <v>0.13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="O51:O53"/>
+    <mergeCell ref="O54:O59"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="O47:O50"/>
-    <mergeCell ref="O51:O53"/>
-    <mergeCell ref="O54:O59"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>